--- a/excel/maquinas.xlsx
+++ b/excel/maquinas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\produccion_server\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/899bfed8ee2a0bb2/Documentos/produccion_server_pg/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1715D3CE-83FA-411A-A942-841966CFD963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{1715D3CE-83FA-411A-A942-841966CFD963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D5FD53C-81E5-4DFA-A89C-E16AF304B982}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F761AC5-4AF8-4430-A8F5-D7EBA500C260}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>nombre</t>
   </si>
@@ -67,6 +67,9 @@
   </si>
   <si>
     <t>Picapasto junior</t>
+  </si>
+  <si>
+    <t>Picapasto 4 cuchillas</t>
   </si>
 </sst>
 </file>
@@ -98,7 +101,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -121,16 +124,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -445,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32D5D598-B176-428A-9E1B-B93F033A8B6C}">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
@@ -506,6 +521,11 @@
         <v>7</v>
       </c>
     </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
